--- a/tools/importer/reports/import-programming-page.report.xlsx
+++ b/tools/importer/reports/import-programming-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>programming-page</t>
   </si>
   <si>
-    <t>2026-05-25T19:02:14.397Z</t>
+    <t>2026-05-25T19:51:45.868Z</t>
   </si>
   <si>
     <t>Watch Local Channels Online | Sling TV</t>
